--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="ADVERTENCIAS_ESPERADAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADVERTENCIAS_ESPERADAS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -211,7 +211,6 @@
         <t>Apellido/s
 Qué se espera: texto
 Máximo 20 caracteres.
-Elegir de la lista "Provincias".
 Campo obligatorio.</t>
       </text>
     </comment>
@@ -985,7 +984,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1132,7 +1131,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1275,7 +1274,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1367,10 +1366,8 @@
           <t>Dato 3</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
+      <c r="V6" s="10" t="n">
+        <v>46546</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1379,22 +1376,22 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Secundaria completa</t>
+          <t>Pre escolar</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1403,11 +1400,11 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46581</v>
+        <v>45812</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1422,12 +1419,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1437,7 +1434,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1446,11 +1443,11 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>45636</v>
+        <v>46213</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1470,7 +1467,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1550,7 +1547,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>45717</v>
+        <v>46287</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1565,7 +1562,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1708,12 +1705,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CABA</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1771,18 +1768,18 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Dispositivo no declarado</t>
         </is>
       </c>
       <c r="P9" s="4" t="n">
         <v>6</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1800,10 +1797,8 @@
           <t>Dato 6</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
+      <c r="V9" s="10" t="n">
+        <v>46292</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1812,12 +1807,12 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1827,23 +1822,27 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Universitario completo</t>
+          <t>Terciario incompleto</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>46297</v>
+        <v>45829</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr"/>
+          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 6</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1851,12 +1850,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1866,20 +1865,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>OPN</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>45774</v>
+        <v>45646</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1899,29 +1898,29 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="P10" s="4" t="n">
         <v>7</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1935,7 +1934,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Familia Sosa</t>
+          <t>Familia Quiroga</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1945,7 +1944,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1979,7 +1978,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45867</v>
+        <v>45739</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1994,7 +1993,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CABA</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2137,7 +2136,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2220,17 +2219,17 @@
       <c r="T12" s="10" t="n">
         <v>46305</v>
       </c>
-      <c r="U12" s="10" t="n">
-        <v>46295</v>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dato 9</t>
+        </is>
+      </c>
+      <c r="V12" s="10" t="n">
+        <v>46306</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2240,22 +2239,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Jardín de infantes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Jardín de infantes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="AC12" s="5" t="n">
@@ -2263,7 +2262,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -2274,12 +2273,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Misiones</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2289,22 +2288,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Policía</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>46231</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OPN</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>45597</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>Dato 10</t>
@@ -2322,7 +2321,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2332,23 +2331,23 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>Hogar Los Álamos</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="P13" s="4" t="n">
         <v>10</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2358,7 +2357,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Familia Martínez</t>
+          <t>Familia Ojeda</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2368,12 +2367,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2383,30 +2382,30 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Terciario incompleto</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Primaria completa</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC13" s="5" t="n">
-        <v>45661</v>
+        <v>46287</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Cese por guarda con fines de adopción</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -2417,12 +2416,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2437,11 +2436,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>45733</v>
+        <v>45723</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2465,33 +2464,33 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P14" s="4" t="n">
         <v>11</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2501,7 +2500,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Familia Paz</t>
+          <t>Familia Díaz</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2516,19 +2515,19 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>No</t>
@@ -2541,11 +2540,11 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45850</v>
+        <v>45823</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2560,12 +2559,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2575,7 +2574,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2584,11 +2583,11 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>45731</v>
+        <v>45788</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2603,7 +2602,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2613,7 +2612,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2630,7 +2629,7 @@
         <v>12</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2644,16 +2643,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Familia López</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Dato 12</t>
-        </is>
-      </c>
-      <c r="V15" s="10" t="n">
-        <v>46337</v>
+          <t>Familia Gómez</t>
+        </is>
+      </c>
+      <c r="U15" s="10" t="n">
+        <v>46299</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hogar Nuestra Señora</t>
+        </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2662,38 +2661,42 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Primaria incompleta</t>
+          <t>Pre escolar</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>46290</v>
+        <v>45941</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr"/>
+          <t>Cese por guarda con fines de adopción</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 12</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2701,12 +2704,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2716,7 +2719,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2725,11 +2728,11 @@
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>46015</v>
+        <v>45703</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2744,7 +2747,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2754,28 +2757,28 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="P16" s="4" t="n">
         <v>13</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2785,7 +2788,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Familia Gómez</t>
+          <t>Familia Ledesma</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2795,32 +2798,32 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Terciario completo</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2829,7 +2832,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46049</v>
+        <v>45765</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2844,12 +2847,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Entre Ríos</t>
+          <t>López</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2859,22 +2862,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Justicia</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>45818</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>Salud</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>OPN</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>45838</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Juzgado</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>Dato 14</t>
@@ -2887,17 +2890,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2907,14 +2910,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P17" s="4" t="n">
         <v>14</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2928,7 +2931,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Familia López</t>
+          <t>Familia Quiroga</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2938,12 +2941,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2953,17 +2956,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Pre escolar</t>
+          <t>Primaria incompleta</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2972,11 +2975,11 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45911</v>
+        <v>45891</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Otros motivos de cese de la MPE</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -2987,7 +2990,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3002,20 +3005,20 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>45786</v>
+        <v>45607</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3035,89 +3038,89 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P18" s="4" t="n">
         <v>15</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
+          <t>Centro Municipal Norte</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="n">
+        <v>46298</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Familia Martínez</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>Dato 15</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Familia Villalba</t>
-        </is>
-      </c>
-      <c r="U18" s="10" t="n">
-        <v>46297</v>
-      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Pre escolar</t>
+          <t>Universitario completo</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46628</v>
+        <v>45678</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
+          <t>Cese por guarda con fines de adopción</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
@@ -3128,12 +3131,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3143,20 +3146,20 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>46071</v>
+        <v>46018</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3171,38 +3174,38 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="P19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3227,40 +3230,40 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Pre escolar</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Nunca asistió</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC19" s="5" t="n">
-        <v>46260</v>
+        <v>46051</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Cese por guarda con fines de adopción</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
@@ -3271,12 +3274,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3286,22 +3289,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Encuentro espontáneo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Justicia</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>OPN</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>46013</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Educación</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>Dato 17</t>
@@ -3314,96 +3317,96 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>Hogar Nuestra Señora</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Dato 17</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Familia Cabrera</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dato 17</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>Residencia El Ceibo</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Dato 17</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Familia Paz</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Dato 17</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Nunca asistió</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Nunca asistió</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AC20" s="5" t="n">
-        <v>46063</v>
+        <v>46260</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
@@ -3414,12 +3417,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Formosa</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3429,83 +3432,79 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Justicia</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Policía</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Dato 18</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Dato 18</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>Otro</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>45877</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Dato 18</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Dato 18</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar convenido (sin declarar)</t>
         </is>
       </c>
       <c r="P21" s="4" t="n">
         <v>18</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>46558</v>
+      </c>
+      <c r="S21" s="10" t="n">
+        <v>46300</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Familia Gómez</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>Dato 18</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Familia Gómez</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Dato 18</t>
-        </is>
-      </c>
       <c r="V21" t="inlineStr">
         <is>
           <t>Hogar Los Álamos</t>
@@ -3513,40 +3512,40 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Secundaria completa</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>46008</v>
+        <v>46287</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Cese por guarda con fines de adopción</t>
+          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
@@ -3557,12 +3556,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3577,15 +3576,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OPN</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>45840</v>
+        <v>45666</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3600,12 +3599,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3620,18 +3619,18 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="P22" s="4" t="n">
         <v>19</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3641,7 +3640,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Familia Ledesma</t>
+          <t>Familia Gómez</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3651,17 +3650,17 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3671,28 +3670,32 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Primaria completa</t>
+          <t>Universitario completo</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45945</v>
+        <v>45826</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
           <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 19</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -3700,12 +3703,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3715,20 +3718,20 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>OPN</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>46090</v>
+        <v>45767</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3753,70 +3756,70 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="P23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>Residencia El Ceibo</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Dato 20</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Familia Martínez</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dato 20</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Dato 20</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Familia Quiroga</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Dato 20</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Universitario incompleto</t>
@@ -3828,14 +3831,18 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>46258</v>
+        <v>45845</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr"/>
+          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 20</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -3843,12 +3850,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Corrientes</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Martina</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3867,7 +3874,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>46113</v>
+        <v>45665</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3886,7 +3893,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3896,12 +3903,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3913,54 +3920,54 @@
         <v>21</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
+          <t>Programa de Acompañamiento Sur</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="n">
+        <v>46294</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>Dato 21</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Familia Martínez</t>
-        </is>
-      </c>
-      <c r="U24" s="10" t="n">
-        <v>46345</v>
-      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Universitario incompleto</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3969,14 +3976,18 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>46390</v>
+        <v>45728</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Cese por guarda con fines de adopción</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr"/>
+          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 21</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -3984,12 +3995,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Misiones</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3999,50 +4010,50 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Justicia</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>45862</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Dato 22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Dato 22</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>Otro</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n">
-        <v>45756</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Policía</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Dato 22</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Dato 22</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Familia ampliada</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4054,11 +4065,11 @@
         <v>22</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -4078,12 +4089,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -4093,33 +4104,37 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Terciario completo</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC25" s="5" t="n">
-        <v>45897</v>
+        <v>45981</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr"/>
+          <t>Cese por guarda con fines de adopción</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 22</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -4127,12 +4142,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tucumán</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4142,22 +4157,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Encuentro espontáneo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Justicia</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>46150</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>Policía</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Justicia</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>46021</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Educación</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>Dato 23</t>
@@ -4175,33 +4190,33 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P26" s="4" t="n">
         <v>23</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4211,7 +4226,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Familia Cabrera</t>
+          <t>Familia Romero</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4221,48 +4236,52 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Terciario incompleto</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Terciario completo</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC26" s="5" t="n">
-        <v>46057</v>
+        <v>46287</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
           <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 23</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -4270,12 +4289,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Corrientes</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4285,7 +4304,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4294,11 +4313,11 @@
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>45948</v>
+        <v>45836</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4313,37 +4332,39 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="P27" s="4" t="n">
         <v>24</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="R27" s="10" t="n">
-        <v>46584</v>
+        <v>41</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Hogar Nuestra Señora</t>
+        </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4352,15 +4373,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Familia Sosa</t>
-        </is>
-      </c>
-      <c r="U27" s="10" t="n">
-        <v>46376</v>
+          <t>Familia Fernández</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dato 24</t>
+        </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4370,42 +4393,38 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Nunca asistió</t>
+          <t>Pre escolar</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46035</v>
+        <v>46291</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
           <t>Cese por mayoría de edad SIN proyecto autónomo</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 24</t>
-        </is>
-      </c>
+      <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -4413,7 +4432,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4433,15 +4452,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OPN</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>45649</v>
+        <v>45688</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4461,87 +4480,87 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
+          <t>Programa de Acompañamiento Sur</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="P28" s="4" t="n">
         <v>25</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>Centro Municipal Norte</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Dato 25</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Familia Ojeda</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dato 25</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Dato 25</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Familia López</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Dato 25</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Terciario incompleto</t>
+          <t>Terciario completo</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45736</v>
+        <v>45745</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4556,12 +4575,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Misiones</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4571,20 +4590,20 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>OPN</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>46267</v>
+        <v>45888</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4604,12 +4623,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4619,83 +4638,79 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="P29" s="4" t="n">
         <v>26</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>Hogar Nuestra Señora</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Dato 26</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Familia Quiroga</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dato 26</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>Hogar Los Álamos</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Dato 26</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Familia Ojeda</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Dato 26</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Nunca asistió</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Pre escolar</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC29" s="5" t="n">
-        <v>46287</v>
+        <v>46053</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
           <t>Cese por mayoría de edad SIN proyecto autónomo</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 26</t>
-        </is>
-      </c>
+      <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -4703,12 +4718,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4723,15 +4738,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>OPN</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>46115</v>
+        <v>45821</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4746,22 +4761,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4773,31 +4788,33 @@
         <v>27</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>Hogar Los Álamos</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Dato 27</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Familia Cabrera</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Dato 27</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>Hogar Nuestra Señora</t>
         </is>
       </c>
-      <c r="S30" s="10" t="n">
-        <v>46289</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Familia Romero</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Dato 27</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Reintegro familiar</t>
@@ -4805,42 +4822,38 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Jardín de infantes</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Primaria incompleta</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC30" s="5" t="n">
-        <v>46287</v>
+        <v>45832</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 27</t>
-        </is>
-      </c>
+          <t>Cese por guarda con fines de adopción</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -4848,12 +4861,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4872,11 +4885,11 @@
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>46244</v>
+        <v>46130</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4891,7 +4904,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4901,24 +4914,24 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P31" s="4" t="n">
         <v>28</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -4932,7 +4945,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Familia Gómez</t>
+          <t>Familia Ojeda</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4942,37 +4955,37 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Universitario completo</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC31" s="5" t="n">
@@ -4991,12 +5004,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5006,20 +5019,20 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>46010</v>
+        <v>45697</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5034,7 +5047,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -5044,12 +5057,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5061,33 +5074,33 @@
         <v>29</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>Residencia El Ceibo</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Dato 29</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Dato 29</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
           <t>Centro Municipal Norte</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Dato 29</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Familia Paz</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Dato 29</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Reintegro familiar</t>
@@ -5095,35 +5108,35 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Terciario completo</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Terciario incompleto</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AC32" s="5" t="n">
-        <v>46167</v>
+        <v>45867</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
@@ -5134,12 +5147,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5158,7 +5171,7 @@
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>45923</v>
+        <v>45843</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -5177,38 +5190,38 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P33" s="4" t="n">
         <v>30</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -5216,10 +5229,8 @@
           <t>Dato 30</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Familia Fernández</t>
-        </is>
+      <c r="T33" s="10" t="n">
+        <v>46297</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -5228,12 +5239,12 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -5243,7 +5254,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -5253,23 +5264,27 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
+          <t>Primaria completa</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC33" s="5" t="n">
-        <v>46491</v>
+        <v>45906</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr"/>
+          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 30</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -6472,10 +6487,7 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="W2:Y2"/>
   </mergeCells>
-  <dataValidations count="14">
-    <dataValidation sqref="B4:B203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Apellido/s&quot;." type="list">
-      <formula1>LISTAS!$G$2:$G$25</formula1>
-    </dataValidation>
+  <dataValidations count="13">
     <dataValidation sqref="E4:E203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Origen de la demanda&quot;." type="list">
       <formula1>LISTAS!$E$2:$E$7</formula1>
     </dataValidation>
@@ -6495,7 +6507,7 @@
       <formula1>LISTAS!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="W4:W203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de proyecto de restitución&quot;." type="list">
-      <formula1>LISTAS!$H$2:$H$5</formula1>
+      <formula1>LISTAS!$G$2:$G$5</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Decreto judicial de adoptabilidad&quot;." type="list">
       <formula1>LISTAS!$F$2:$F$4</formula1>
@@ -6576,8 +6588,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Campo obligatorio.
-Debe elegirse un valor de la lista "Provincias".</t>
+          <t>Campo obligatorio.</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6955,7 +6966,6 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6991,11 +7001,6 @@
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>Provincias</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
           <t>Tipo de proyecto de restitución</t>
         </is>
       </c>
@@ -7033,11 +7038,6 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>Reintegro familiar</t>
         </is>
       </c>
@@ -7075,11 +7075,6 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CABA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>Adopción</t>
         </is>
       </c>
@@ -7117,11 +7112,6 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Catamarca</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>Autonomía</t>
         </is>
       </c>
@@ -7149,11 +7139,6 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaco</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>Otros</t>
         </is>
       </c>
@@ -7174,11 +7159,6 @@
           <t>Juzgado</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7191,11 +7171,6 @@
           <t>Otros</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7203,11 +7178,6 @@
           <t>Secundaria completa</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Corrientes</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7215,11 +7185,6 @@
           <t>Terciario incompleto</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Entre Ríos</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7227,11 +7192,6 @@
           <t>Terciario completo</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Formosa</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7239,11 +7199,6 @@
           <t>Universitario incompleto</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Jujuy</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7251,105 +7206,11 @@
           <t>Universitario completo</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>La Pampa</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>La Rioja</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Mendoza</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Misiones</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Neuquén</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Río Negro</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Salta</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>San Juan</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>San Luis</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Santiago del Estero</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Tierra del Fuego</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Tucumán</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7406,12 +7267,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fecha de cese</t>
+          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mpe_fecha_de_cese_comparar_valor</t>
+          <t>mpe_departamento_de_residencia_de_la_familia_dispositivo_fami_e8c08b_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7426,12 +7287,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fecha de cese</t>
+          <t>Nombre de la residencia/hogar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mpe_fecha_de_cese_comparar_valor</t>
+          <t>mpe_residencia_existe_en_archivo</t>
         </is>
       </c>
     </row>
@@ -7442,16 +7303,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ID familia ampliada</t>
+          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>mpe_id_familia_ampliada_comparar_valor</t>
+          <t>mpe_departamento_de_residencia_de_la_familia_dispositivo_fami_e8c08b_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7327,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Familia Ampliada</t>
+          <t>ID familia ampliada</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>mpe_familia_ampliada_comparar_valor</t>
+          <t>mpe_id_familia_ampliada_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7486,12 +7347,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vínculo con el NyA</t>
+          <t>Familia Ampliada</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mpe_vinculo_con_el_nya_comparar_valor</t>
+          <t>mpe_familia_ampliada_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7363,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7526,12 +7387,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fecha de cese</t>
+          <t>Vínculo con el NyA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>mpe_fecha_de_cese_comparar_valor</t>
+          <t>mpe_vinculo_con_el_nya_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7407,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vínculo con el NyA</t>
+          <t>ID familia ampliada</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>mpe_vinculo_con_el_nya_comparar_valor</t>
+          <t>mpe_id_familia_ampliada_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7562,16 +7423,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fecha de cese</t>
+          <t>Nombre de la residencia/hogar</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>mpe_fecha_de_cese_comparar_valor</t>
+          <t>mpe_residencia_existe_en_archivo</t>
         </is>
       </c>
     </row>
@@ -7582,16 +7443,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vínculo con el NyA</t>
+          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>mpe_vinculo_con_el_nya_comparar_valor</t>
+          <t>mpe_departamento_de_residencia_de_la_familia_dispositivo_fami_597d04_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7602,16 +7463,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fecha de cese</t>
+          <t>ID familia ampliada</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>mpe_fecha_de_cese_comparar_valor</t>
+          <t>mpe_id_familia_ampliada_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7622,16 +7483,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
+          <t>ID familia ampliada</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>mpe_departamento_de_residencia_de_la_familia_dispositivo_fami_597d04_comparar_valor</t>
+          <t>mpe_id_familia_ampliada_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7646,12 +7507,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vínculo con el NyA</t>
+          <t>Fecha de cese</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>mpe_vinculo_con_el_nya_comparar_valor</t>
+          <t>mpe_fecha_de_cese_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7662,36 +7523,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ID familia ampliada</t>
+          <t>Familia Ampliada</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>mpe_id_familia_ampliada_comparar_valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>33</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Fecha de cese</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>mpe_fecha_de_cese_comparar_valor</t>
+          <t>mpe_familia_ampliada_comparar_valor</t>
         </is>
       </c>
     </row>

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,7 +112,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -203,7 +203,7 @@
       <text>
         <t>ID del Niño, niña o Adolescente
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
@@ -824,155 +824,155 @@
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+          <t>ID del Niño, niña o Adolescente *</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Apellido/s *</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Nombre/s *</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Cuil o documento de identidad *</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Origen de la demanda</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Organismo que toma la MPE</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Fecha de inicio MPE</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Última fecha de renovación</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Motivo de toma de MPE</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Submotivo de toma de MPE</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Elevación dictamen MPE a juzgado</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Control de legalidad por autoridad judicial</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Modalidad de cuidado</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>ID dispositivo residencial</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Nombre de la residencia/hogar *</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>ID familia</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>Departamento de residencia de la familia (dispositivo familiar)</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>ID familia ampliada</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Familia Ampliada</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Vínculo con el NyA</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>Departamento de residencia de la familia (dispositivo familiar)</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>Tipo de proyecto de restitución</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>Decreto judicial de adoptabilidad</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>Solicitud inclusión proy. autonomía</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>¿Asiste actualmente a una institución educativa?</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Máximo nivel educativo alcanzado</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>Consumo problemático de sustancias</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>Fecha de cese</t>
         </is>
       </c>
-      <c r="AD3" s="2" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <t>Motivo de cese</t>
         </is>
       </c>
-      <c r="AE3" s="2" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="V6" s="10" t="n">
-        <v>46546</v>
+        <v>46547</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="V9" s="10" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45829</v>
+        <v>45830</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45739</v>
+        <v>45740</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="S12" s="10" t="n">
-        <v>46504</v>
+        <v>46505</v>
       </c>
       <c r="T12" s="10" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="V12" s="10" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45823</v>
+        <v>45824</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>45788</v>
+        <v>45789</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="U15" s="10" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45941</v>
+        <v>45942</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>45765</v>
+        <v>45766</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>45818</v>
+        <v>45819</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45891</v>
+        <v>45892</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="S18" s="10" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>46018</v>
+        <v>46019</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
         <v>4</v>
       </c>
       <c r="R21" s="10" t="n">
-        <v>46558</v>
+        <v>46559</v>
       </c>
       <c r="S21" s="10" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>45767</v>
+        <v>45768</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="S24" s="10" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45728</v>
+        <v>45729</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>45836</v>
+        <v>45837</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45745</v>
+        <v>45746</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>45821</v>
+        <v>45822</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>45697</v>
+        <v>45698</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45867</v>
+        <v>45868</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>45843</v>
+        <v>45844</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="T33" s="10" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45906</v>
+        <v>45907</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -6578,7 +6578,11 @@
           <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Campo obligatorio.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADVERTENCIAS_ESPERADAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MPE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="ADVERTENCIAS_ESPERADAS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,10 +36,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -97,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -111,11 +106,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -196,257 +186,252 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
-        <t>ID del Niño, niña o Adolescente
-Qué se espera: un número entero
-Campo obligatorio.</t>
+        <t>ID del niño, niña o adolescente
+Obligatorio
+Qué va: Número entero.
+Tiene que figurar en el LEGAJO_NYA del período.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Apellido/s
-Qué se espera: texto
-Máximo 20 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Nombre/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Cuil o documento de identidad
-Qué se espera: texto
-Máximo 13 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 13 caracteres.
+Tiene que ser un CUIL válido: se controla el dígito verificador.
+Aviso: Con el formato NN-NNNNNNNN-N.
+Tiene que coincidir con el del LEGAJO_NYA.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Origen de la demanda
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Origen de la demanda".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Encuentro espontáneo, Educación, Salud, Policía, Juzgado, Otros.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Organismo que toma la MPE
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Organismo que toma la MPE".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: OPN, Justicia, Otro.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de inicio MPE
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Última fecha de renovación
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Origen de la demanda".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Encuentro espontáneo, Educación, Salud, Policía, Juzgado, Otros.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Motivo de toma de MPE
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Submotivo de toma de MPE
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Elevación dictamen MPE a juzgado
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Control de legalidad por autoridad judicial
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>Modalidad de cuidado
-Qué se espera: texto
-Máximo 22 caracteres.
-Elegir de la lista "Modalidad de cuidado".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Alojamiento formal, Familia ampliada, Familia de acogimiento, Otro.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>ID dispositivo residencial
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Nombre de la residencia/hogar
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.
+Aviso: Tiene que figurar en el DISP_SCP del período.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>ID familia
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 1 y None.
+Entre 1 y 999999999.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Familia
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Departamento de residencia de la familia (dispositivo familiar)
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>ID familia ampliada
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>Familia Ampliada
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Vínculo con el NyA
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>Departamento de residencia de la familia (dispositivo familiar)
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Tipo de proyecto de restitución
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Tipo de proyecto de restitución".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Reintegro familiar, Adopción, Autonomía, Otros.</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>Decreto judicial de adoptabilidad
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Solicitud inclusión proy. autonomía
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>¿Asiste actualmente a una institución educativa?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>Máximo nivel educativo alcanzado
-Qué se espera: texto
-Máximo 24 caracteres.
-Elegir de la lista "Máximo nivel educativo alcanzado".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 12 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="AB3" authorId="0" shapeId="0">
       <text>
         <t>Consumo problemático de sustancias
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="AC3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de cese
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.
+"Fecha de cese" no puede ser anterior a "Fecha de inicio MPE" ()</t>
       </text>
     </comment>
     <comment ref="AD3" authorId="0" shapeId="0">
       <text>
         <t>Motivo de cese
-Qué se espera: texto
-Máximo 56 caracteres.
-Elegir de la lista "Motivo de cese".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Cese por guarda con fines de adopción, Cese por mayoría de edad CON proyecto autónomo (CON PAE), Cese por mayoría de edad CON proyecto autónomo (SIN PAE), Cese por mayoría de edad SIN proyecto autónomo, Otros motivos de cese de la MPE.</t>
       </text>
     </comment>
     <comment ref="AE3" authorId="0" shapeId="0">
       <text>
         <t>Observaciones
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.</t>
       </text>
     </comment>
   </commentList>
@@ -824,7 +809,7 @@
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente *</t>
+          <t>ID del niño, niña o adolescente *</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1008,7 +993,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1112,7 +1097,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1155,7 +1140,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1259,7 +1244,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46151</v>
+        <v>46155</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1298,7 +1283,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>45722</v>
+        <v>45726</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1344,11 +1329,11 @@
         <v>3</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1358,7 +1343,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Familia Gómez</t>
+          <t>Familia Ojeda</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1366,52 +1351,50 @@
           <t>Dato 3</t>
         </is>
       </c>
-      <c r="V6" s="10" t="n">
-        <v>46547</v>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Centro Municipal Norte</t>
+        </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Primaria completa</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Pre escolar</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC6" s="5" t="n">
-        <v>45813</v>
+        <v>45889</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 3</t>
-        </is>
-      </c>
+          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1419,12 +1402,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1434,22 +1417,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>46018</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>46214</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Juzgado</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Dato 4</t>
@@ -1467,33 +1450,33 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>Hogar Nuestra Señora</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>Residencia El Ceibo</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="P7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1503,7 +1486,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Familia Villalba</t>
+          <t>Familia López</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1513,45 +1496,45 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Terciario completo</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Primaria incompleta</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC7" s="5" t="n">
-        <v>46288</v>
+        <v>46194</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -1562,12 +1545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1577,20 +1560,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>45965</v>
+        <v>45881</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1605,38 +1588,38 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>Residencia El Ceibo</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P8" s="4" t="n">
         <v>5</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1646,7 +1629,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Familia Martínez</t>
+          <t>Familia López</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1656,45 +1639,45 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Terciario completo</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Universitario incompleto</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC8" s="5" t="n">
-        <v>46058</v>
+        <v>46073</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
+          <t>Otros motivos de cese de la MPE</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -1705,12 +1688,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ojeda</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Benjamín</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1729,7 +1712,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>45645</v>
+        <v>46179</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1753,17 +1736,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1797,8 +1780,10 @@
           <t>Dato 6</t>
         </is>
       </c>
-      <c r="V9" s="10" t="n">
-        <v>46293</v>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hogar Los Álamos</t>
+        </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1807,42 +1792,38 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Universitario completo</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Terciario incompleto</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC9" s="5" t="n">
-        <v>45830</v>
+        <v>46208</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 6</t>
-        </is>
-      </c>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1850,12 +1831,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ojeda</t>
+          <t>López</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Benjamín</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1865,22 +1846,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Encuentro espontáneo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>46022</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Juzgado</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OPN</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>45647</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Salud</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>Dato 7</t>
@@ -1893,34 +1874,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P10" s="4" t="n">
         <v>7</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1934,7 +1915,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Familia Quiroga</t>
+          <t>Familia López</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1944,12 +1925,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1959,30 +1940,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Universitario incompleto</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Nunca asistió</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC10" s="5" t="n">
-        <v>45740</v>
+        <v>46148</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Cese por guarda con fines de adopción</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -1993,12 +1974,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gómez</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2008,7 +1989,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2017,11 +1998,11 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>46200</v>
+        <v>46232</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2036,7 +2017,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2046,86 +2027,86 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="P11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>Hogar Nuestra Señora</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Dato 8</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Familia Ojeda</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dato 8</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>Residencia El Ceibo</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Dato 8</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Familia Rodríguez</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Dato 8</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
+          <t>Pre escolar</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC11" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Otros motivos de cese de la MPE</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -2136,12 +2117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2151,16 +2132,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OPN</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>46222</v>
+        <v>45626</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2179,7 +2160,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2189,12 +2170,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2206,26 +2187,32 @@
         <v>9</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="n">
-        <v>46505</v>
-      </c>
-      <c r="T12" s="10" t="n">
-        <v>46306</v>
+          <t>Centro Municipal Norte</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Dato 9</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Familia Gómez</t>
+        </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>Dato 9</t>
         </is>
       </c>
-      <c r="V12" s="10" t="n">
-        <v>46307</v>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hogar Nuestra Señora</t>
+        </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2234,12 +2221,12 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2254,15 +2241,15 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>46288</v>
+        <v>45788</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+          <t>Cese por guarda con fines de adopción</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -2273,12 +2260,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2288,66 +2275,66 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Justicia</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Juzgado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dato 10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dato 10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>Otro</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>46232</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Dato 10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Dato 10</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P13" s="4" t="n">
         <v>10</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2357,7 +2344,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Familia Ojeda</t>
+          <t>Familia Ledesma</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2367,7 +2354,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2377,35 +2364,35 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Jardín de infantes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Terciario incompleto</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC13" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
+          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -2416,12 +2403,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2431,20 +2418,20 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>45724</v>
+        <v>46236</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2459,7 +2446,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2479,18 +2466,18 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="P14" s="4" t="n">
         <v>11</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2500,7 +2487,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Familia Díaz</t>
+          <t>Familia Ojeda</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2510,7 +2497,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2520,7 +2507,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2530,25 +2517,25 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Terciario incompleto</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Secundaria completa</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC14" s="5" t="n">
-        <v>45824</v>
+        <v>46292</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
@@ -2559,12 +2546,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2579,61 +2566,61 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>OPN</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>46196</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Dato 12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dato 12</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>Otro</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n">
-        <v>45789</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Educación</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Dato 12</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Dato 12</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Familia ampliada</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P15" s="4" t="n">
         <v>12</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2643,20 +2630,20 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Familia Gómez</t>
-        </is>
-      </c>
-      <c r="U15" s="10" t="n">
-        <v>46300</v>
+          <t>Familia Romero</t>
+        </is>
+      </c>
+      <c r="U15" s="7" t="n">
+        <v>46294</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2666,37 +2653,33 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Primaria incompleta</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Pre escolar</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC15" s="5" t="n">
-        <v>45942</v>
+        <v>46292</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Cese por guarda con fines de adopción</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 12</t>
-        </is>
-      </c>
+          <t>Otros motivos de cese de la MPE</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2704,12 +2687,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2719,22 +2702,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Encuentro espontáneo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OPN</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>45693</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>Policía</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>OPN</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>45704</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Educación</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Dato 13</t>
@@ -2757,89 +2740,93 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>Hogar Los Álamos</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>Hogar Nuestra Señora</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="P16" s="4" t="n">
         <v>13</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>Residencia El Ceibo</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Dato 13</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Dato 13</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
           <t>Hogar Nuestra Señora</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Dato 13</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Familia Ledesma</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Dato 13</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Jardín de infantes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC16" s="5" t="n">
-        <v>45766</v>
+        <v>45757</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr"/>
+          <t>Otros motivos de cese de la MPE</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 13</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -2847,12 +2834,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2862,7 +2849,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2871,11 +2858,11 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>45819</v>
+        <v>45618</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2890,38 +2877,38 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P17" s="4" t="n">
         <v>14</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2931,7 +2918,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Familia Quiroga</t>
+          <t>Familia Martínez</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2941,12 +2928,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2956,30 +2943,30 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Primaria completa</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Primaria incompleta</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC17" s="5" t="n">
-        <v>45892</v>
+        <v>45699</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
+          <t>Cese por guarda con fines de adopción</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -2990,12 +2977,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Villalba</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3005,16 +2992,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>OPN</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>45608</v>
+        <v>45934</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3043,36 +3030,38 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="P18" s="4" t="n">
         <v>15</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="n">
-        <v>46299</v>
+          <t>Hogar Nuestra Señora</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Dato 15</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Familia Martínez</t>
+          <t>Familia Gómez</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -3080,50 +3069,52 @@
           <t>Dato 15</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
+      <c r="V18" s="7" t="n">
+        <v>46526</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Primaria completa</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Universitario completo</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC18" s="5" t="n">
-        <v>45679</v>
+        <v>46089</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Cese por guarda con fines de adopción</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr"/>
+          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 15</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -3136,7 +3127,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3146,7 +3137,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3155,11 +3146,11 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>46019</v>
+        <v>46021</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3174,7 +3165,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3184,24 +3175,24 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="P19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3215,7 +3206,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Familia Cabrera</t>
+          <t>Familia Gómez</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3225,32 +3216,32 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Pre escolar</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3259,14 +3250,18 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>46052</v>
+        <v>46163</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Cese por guarda con fines de adopción</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr"/>
+          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 16</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -3274,12 +3269,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3294,15 +3289,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>46072</v>
+        <v>46139</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3322,33 +3317,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3358,7 +3353,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Familia Cabrera</t>
+          <t>Familia Sosa</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3368,12 +3363,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3383,17 +3378,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Nunca asistió</t>
+          <t>Universitario completo</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3402,11 +3397,11 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>46261</v>
+        <v>46230</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Otros motivos de cese de la MPE</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
@@ -3422,7 +3417,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3432,7 +3427,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3441,11 +3436,11 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>46248</v>
+        <v>46266</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3460,12 +3455,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3475,29 +3470,31 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>Residencia El Ceibo</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Hogar convenido (sin declarar)</t>
         </is>
       </c>
       <c r="P21" s="4" t="n">
         <v>18</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R21" s="10" t="n">
-        <v>46559</v>
-      </c>
-      <c r="S21" s="10" t="n">
-        <v>46301</v>
+        <v>90</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Hogar Los Álamos</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="n">
+        <v>46336</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Familia Gómez</t>
+          <t>Familia Paz</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3507,7 +3504,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3517,31 +3514,31 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Nunca asistió</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Nunca asistió</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC21" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3556,12 +3553,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3571,7 +3568,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3580,11 +3577,11 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>45667</v>
+        <v>45932</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3599,7 +3596,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3609,12 +3606,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3626,11 +3623,11 @@
         <v>19</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3640,7 +3637,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Familia Gómez</t>
+          <t>Familia Ledesma</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3650,45 +3647,45 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Universitario completo</t>
+          <t>Secundaria incompleta</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45827</v>
+        <v>46013</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -3703,7 +3700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3718,16 +3715,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>45768</v>
+        <v>46097</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3746,34 +3743,34 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -3787,7 +3784,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Familia Martínez</t>
+          <t>Familia Sosa</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3802,7 +3799,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3812,17 +3809,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Universitario incompleto</t>
+          <t>Secundaria incompleta</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3831,11 +3828,11 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45846</v>
+        <v>46129</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3850,12 +3847,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3865,74 +3862,76 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Justicia</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>45724</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Dato 21</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Dato 21</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>Otro</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n">
-        <v>45666</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Dato 21</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Dato 21</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P24" s="4" t="n">
         <v>21</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="n">
-        <v>46295</v>
+          <t>Hogar Nuestra Señora</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Dato 21</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Familia Fernández</t>
+          <t>Familia Paz</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3942,7 +3941,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3952,42 +3951,38 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Nunca asistió</t>
+          <t>Universitario incompleto</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45729</v>
+        <v>45892</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 21</t>
-        </is>
-      </c>
+          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -3995,12 +3990,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Benjamín</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4010,20 +4005,20 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>OPN</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>45863</v>
+        <v>45768</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4048,28 +4043,28 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P25" s="4" t="n">
         <v>22</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -4079,7 +4074,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Familia Villalba</t>
+          <t>Familia Sosa</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4094,47 +4089,43 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Primaria incompleta</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AC25" s="5" t="n">
-        <v>45982</v>
+        <v>45775</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
           <t>Cese por guarda con fines de adopción</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 22</t>
-        </is>
-      </c>
+      <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -4142,12 +4133,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4166,11 +4157,11 @@
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>46151</v>
+        <v>45867</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4190,12 +4181,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4205,18 +4196,18 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="P26" s="4" t="n">
         <v>23</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4226,7 +4217,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Familia Romero</t>
+          <t>Familia Villalba</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4236,45 +4227,45 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Terciario incompleto</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC26" s="5" t="n">
-        <v>46288</v>
+        <v>45986</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
+          <t>Cese por guarda con fines de adopción</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -4289,12 +4280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>López</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4304,20 +4295,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>45837</v>
+        <v>45748</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4342,24 +4333,24 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P27" s="4" t="n">
         <v>24</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -4373,55 +4364,53 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Familia Fernández</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Dato 24</t>
-        </is>
+          <t>Familia Díaz</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="n">
+        <v>46607</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Pre escolar</t>
+          <t>Terciario incompleto</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>46292</v>
+        <v>45931</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
@@ -4432,12 +4421,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4447,20 +4436,20 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>45689</v>
+        <v>46209</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4480,7 +4469,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -4490,45 +4479,45 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P28" s="4" t="n">
         <v>25</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>Programa de Acompañamiento Sur</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Dato 25</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Familia Romero</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dato 25</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>Centro Municipal Norte</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Dato 25</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Familia Ojeda</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Dato 25</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Otros</t>
@@ -4536,38 +4525,42 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Terciario completo</t>
+          <t>Secundaria completa</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45746</v>
+        <v>46292</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad SIN proyecto autónomo</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr"/>
+          <t>Otros motivos de cese de la MPE</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 25</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -4575,12 +4568,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4590,20 +4583,20 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OPN</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>45889</v>
+        <v>45803</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4618,12 +4611,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4633,19 +4626,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P29" s="4" t="n">
         <v>26</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -4659,7 +4652,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Familia Quiroga</t>
+          <t>Familia Ojeda</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4669,41 +4662,41 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Nunca asistió</t>
+          <t>Secundaria completa</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>46054</v>
+        <v>45811</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4718,12 +4711,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4733,20 +4726,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OPN</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>45822</v>
+        <v>45714</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4761,38 +4754,38 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar convenido (sin declarar)</t>
         </is>
       </c>
       <c r="P30" s="4" t="n">
         <v>27</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4802,7 +4795,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Familia Cabrera</t>
+          <t>Familia Martínez</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4810,14 +4803,12 @@
           <t>Dato 27</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
-        </is>
+      <c r="V30" s="7" t="n">
+        <v>46304</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -4832,21 +4823,21 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Nunca asistió</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Jardín de infantes</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AC30" s="5" t="n">
-        <v>45833</v>
+        <v>45853</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4866,7 +4857,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4885,11 +4876,11 @@
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>46131</v>
+        <v>46250</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4909,7 +4900,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4931,11 +4922,11 @@
         <v>28</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4945,7 +4936,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Familia Ojeda</t>
+          <t>Familia Díaz</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4955,7 +4946,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4965,22 +4956,22 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Secundaria incompleta</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4989,14 +4980,18 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr"/>
+          <t>Otros motivos de cese de la MPE</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 28</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -5004,12 +4999,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5019,7 +5014,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5028,11 +5023,11 @@
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>45698</v>
+        <v>46181</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5047,60 +5042,60 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P32" s="4" t="n">
         <v>29</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>Hogar Nuestra Señora</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Dato 29</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Familia Cabrera</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Dato 29</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
           <t>Residencia El Ceibo</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Dato 29</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Familia Fernández</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Dato 29</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Reintegro familiar</t>
@@ -5113,30 +5108,30 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Universitario incompleto</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Terciario completo</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC32" s="5" t="n">
-        <v>45868</v>
+        <v>46292</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Cese por guarda con fines de adopción</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
@@ -5147,12 +5142,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5167,15 +5162,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OPN</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>45844</v>
+        <v>46183</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -5190,58 +5185,60 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Residencia en trámite de habilitación</t>
         </is>
       </c>
       <c r="P33" s="4" t="n">
         <v>30</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
+          <t>Programa de Acompañamiento Sur</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Dato 30</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Familia Paz</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Dato 30</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
           <t>Hogar Nuestra Señora</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Dato 30</t>
-        </is>
-      </c>
-      <c r="T33" s="10" t="n">
-        <v>46298</v>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Dato 30</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Autonomía</t>
@@ -5273,7 +5270,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45907</v>
+        <v>46246</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -6489,43 +6486,43 @@
   </mergeCells>
   <dataValidations count="13">
     <dataValidation sqref="E4:E203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Origen de la demanda&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$7</formula1>
+      <formula1>Listas!$E$2:$E$7</formula1>
     </dataValidation>
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Organismo que toma la MPE&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="H4:H203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Última fecha de renovación&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$7</formula1>
+      <formula1>Listas!$E$2:$E$7</formula1>
     </dataValidation>
     <dataValidation sqref="K4:K203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Elevación dictamen MPE a juzgado&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="L4:L203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Control de legalidad por autoridad judicial&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Modalidad de cuidado&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="W4:W203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de proyecto de restitución&quot;." type="list">
-      <formula1>LISTAS!$G$2:$G$5</formula1>
+      <formula1>Listas!$G$2:$G$5</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Decreto judicial de adoptabilidad&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="Y4:Y203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Solicitud inclusión proy. autonomía&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z4:Z203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Asiste actualmente a una institución educativa?&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="AA4:AA203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Máximo nivel educativo alcanzado&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$13</formula1>
+      <formula1>Listas!$A$2:$A$13</formula1>
     </dataValidation>
     <dataValidation sqref="AB4:AB203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Consumo problemático de sustancias&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="AD4:AD203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Motivo de cese&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6534,427 +6531,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Indicación para el llenado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Hoja: MPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>NyA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Apellido/s</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Nombre/s</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cuil o documento de identidad</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Medida de Protección Expcecional (MPE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Origen de la demanda</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Origen de la demanda".</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Organismo que toma la MPE</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Organismo que toma la MPE".</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fecha de inicio MPE</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Última fecha de renovación</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Origen de la demanda".</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Motivo de toma de MPE</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Submotivo de toma de MPE</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Elevación dictamen MPE a juzgado</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Control de legalidad por autoridad judicial</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Modalidad de cuidado</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Modalidad de cuidado".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Modalidad formal residencial</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ID dispositivo residencial</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Nombre de la residencia/hogar</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Modalidad Formal Familiar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ID familia</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Familia</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Modalidad Familia Ampliada</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ID familia ampliada</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Familia Ampliada</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Vínculo con el NyA</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Proyecto de Restitución</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Tipo de proyecto de restitución</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Tipo de proyecto de restitución".</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Decreto judicial de adoptabilidad</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Solicitud inclusión proy. autonomía</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Situación del NyA</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>¿Asiste actualmente a una institución educativa?</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Máximo nivel educativo alcanzado</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Máximo nivel educativo alcanzado".</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Consumo problemático de sustancias</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Cese de MPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Fecha de cese</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Motivo de cese</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Motivo de cese".</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7223,13 +6799,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7267,16 +6843,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
+          <t>Nombre de la residencia/hogar</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mpe_departamento_de_residencia_de_la_familia_dispositivo_fami_e8c08b_comparar_valor</t>
+          <t>mpe_residencia_existe_en_archivo</t>
         </is>
       </c>
     </row>
@@ -7287,16 +6863,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nombre de la residencia/hogar</t>
+          <t>Vínculo con el NyA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mpe_residencia_existe_en_archivo</t>
+          <t>mpe_vinculo_con_el_nya_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7307,7 +6883,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -7327,7 +6903,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7347,16 +6923,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Familia Ampliada</t>
+          <t>Vínculo con el NyA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mpe_familia_ampliada_comparar_valor</t>
+          <t>mpe_vinculo_con_el_nya_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7367,16 +6943,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
+          <t>Nombre de la residencia/hogar</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>mpe_departamento_de_residencia_de_la_familia_dispositivo_fami_e8c08b_comparar_valor</t>
+          <t>mpe_residencia_existe_en_archivo</t>
         </is>
       </c>
     </row>
@@ -7387,16 +6963,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vínculo con el NyA</t>
+          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>mpe_vinculo_con_el_nya_comparar_valor</t>
+          <t>mpe_departamento_de_residencia_de_la_familia_dispositivo_fami_e8c08b_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -7407,136 +6983,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ID familia ampliada</t>
+          <t>Nombre de la residencia/hogar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>mpe_id_familia_ampliada_comparar_valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>21</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nombre de la residencia/hogar</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
           <t>mpe_residencia_existe_en_archivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>21</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>mpe_departamento_de_residencia_de_la_familia_dispositivo_fami_597d04_comparar_valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>21</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ID familia ampliada</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>mpe_id_familia_ampliada_comparar_valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>24</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ID familia ampliada</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>mpe_id_familia_ampliada_comparar_valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>27</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Fecha de cese</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>mpe_fecha_de_cese_comparar_valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>33</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Familia Ampliada</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>mpe_familia_ampliada_comparar_valor</t>
         </is>
       </c>
     </row>
